--- a/template_motoristas.xlsx
+++ b/template_motoristas.xlsx
@@ -26,23 +26,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -51,17 +50,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E40AF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,16 +64,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
@@ -93,15 +82,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,135 +454,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚠  INSTRUÇÕES: Preencha a partir da linha 4. Status: Ativo ou Inativo. Classificação: Próprio ou Agregado. Validade CNH: dd/mm/yyyy ou yyyy-mm-dd.</t>
+          <t>CPF</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>APELIDO</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MATRÍCULA</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nº CNH</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>VALIDADE CNH</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CLASSIFICAÇÃO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CPF *</t>
+          <t>123.456.789-00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>NOME *</t>
+          <t>João da Silva</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>APELIDO</t>
+          <t>João</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>MAT001</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>CELULAR</t>
+          <t>(11) 91234-5678</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>E-MAIL</t>
+          <t>joao@email.com</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Nº CNH</t>
+          <t>01234567890</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>VALIDADE CNH</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>CLASSIFICAÇÃO</t>
+          <t>Motorista A</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>123.456.789-00</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>João da Silva</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>João</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT001</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>(11)99999-0000</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>joao@empresa.com.br</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>12345678900</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>31/12/2027</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Próprio</t>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>⚠ Preencha a partir da linha 2. A linha 2 é um exemplo e pode ser apagada.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A4:J4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
